--- a/Data_Pulls/Shiftlens Data Export.xlsx
+++ b/Data_Pulls/Shiftlens Data Export.xlsx
@@ -9278,7 +9278,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -9310,15 +9310,15 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Indirect Care Uplift Pct</v>
+        <v>Flexible Start Times</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>no</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Flexible Start Times</v>
+        <v>Flexible Shift Count</v>
       </c>
       <c r="B5" t="str">
         <v>no</v>
@@ -9326,7 +9326,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Flexible Shift Count</v>
+        <v>Flexible Shift Lengths</v>
       </c>
       <c r="B6" t="str">
         <v>no</v>
@@ -9334,15 +9334,39 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Flexible Shift Lengths</v>
-      </c>
-      <c r="B7" t="str">
-        <v>no</v>
+        <v>Boarding Ratio (RN : Medical Boarders)</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BH Boarding Ratio (RN : BH Boarders)</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Hours Per FTE Mode</v>
+      </c>
+      <c r="B9" t="str">
+        <v>weekly</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Hours Per FTE Value</v>
+      </c>
+      <c r="B10">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>